--- a/patient_registration_form_templates/043_new_patient_registration_dental_hygiene_ucba--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/043_new_patient_registration_dental_hygiene_ucba--patient_registration_form_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,13 +515,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>General Info</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>full name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your full name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -538,13 +542,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>medical history</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please describe your medical history</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -561,13 +569,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Patient Info</t>
+          <t>new patient info</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,13 +592,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>contact details</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide your contact details</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -607,13 +619,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dental History</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>dental history</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your dental history</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -630,13 +646,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allergies</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>allergies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please list your allergies</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,18 +668,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medications</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>medications</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please list your medications</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +695,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>new_patient_info</t>
+          <t>patient_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New Patient Info</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>patient info</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide additional patient information</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,18 +722,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medications</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Medical History 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please describe your medical history</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,18 +749,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_history_2</t>
+          <t>dental_history_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Dental History 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide your dental history</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -740,18 +776,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>new_patient_info_2</t>
+          <t>medications_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New Patient Info</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Medications 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please list your medications</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,18 +803,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_details_2</t>
+          <t>medical_info</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>medical info</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide additional medical information</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,18 +830,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dental_history_2</t>
+          <t>patient_info_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dental History</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Patient Info 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide additional patient information</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -809,18 +857,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>allergies_2</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allergies</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>contact info</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide contact information</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -832,18 +884,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_history_3</t>
+          <t>dental_info</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>dental info</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide dental information</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -855,18 +911,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>new_patient_info_3</t>
+          <t>medical_info_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Patient Info</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Medical Info 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide additional medical information</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -878,18 +938,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_details_3</t>
+          <t>allergies_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Allergies 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please list your allergies</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -901,179 +965,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dental_history_3</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dental History</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>submit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please submit your registration</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>medications_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Medications</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>medical_history_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>new_patient_info_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>New Patient Info</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact_details_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>dental_history_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Dental History</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>allergies_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Allergies</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>medical_history_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
